--- a/output/pdf_financials_xlsx/LA.xlsx
+++ b/output/pdf_financials_xlsx/LA.xlsx
@@ -6270,19 +6270,19 @@
         <v>0</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>7.495181</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>7.907501</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>5.582702</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>5.713944</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>5.657059</v>
       </c>
     </row>
     <row r="93">
@@ -11275,7 +11275,11 @@
           <t>Reserve 8</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LA.xlsx
+++ b/output/pdf_financials_xlsx/LA.xlsx
@@ -1092,31 +1092,31 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00345</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002679</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.005874</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000239</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000503</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000472</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.009767</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.00728</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.035829</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1125,13 +1125,13 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.316866</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>1.400865</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>1.046427</v>
       </c>
     </row>
     <row r="13">
@@ -2142,31 +2142,31 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.750603</v>
+        <v>-0.754053</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.451414</v>
+        <v>-0.454093</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.450353</v>
+        <v>-0.456227</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.689428</v>
+        <v>-0.689667</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.857778</v>
+        <v>-0.858281</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.699369</v>
+        <v>-0.699841</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.729725</v>
+        <v>-0.739492</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.959579</v>
+        <v>-0.966859</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.626378</v>
+        <v>-0.662207</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-2.05707</v>
@@ -2175,13 +2175,13 @@
         <v>-8.06756</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.917599</v>
+        <v>-2.234465</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.607535</v>
+        <v>-2.0084</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-3.995122</v>
+        <v>-5.041549</v>
       </c>
     </row>
     <row r="28">
@@ -2270,31 +2270,31 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.742587</v>
+        <v>-0.746037</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.443819</v>
+        <v>-0.446498</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.44101</v>
+        <v>-0.446884</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.679882</v>
+        <v>-0.680121</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.847066</v>
+        <v>-0.847569</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.69435</v>
+        <v>-0.6948220000000001</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.729583</v>
+        <v>-0.73935</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.959579</v>
+        <v>-0.966859</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.622039</v>
+        <v>-0.657868</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-1.940943</v>
@@ -2303,13 +2303,13 @@
         <v>-7.950716</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.720165</v>
+        <v>-2.037031</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.459803</v>
+        <v>-1.860668</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-3.842036</v>
+        <v>-4.888463</v>
       </c>
     </row>
     <row r="30">
@@ -2614,10 +2614,10 @@
         <v>1.390162</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>8.772845999999999</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>6.31809</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>34.54586</v>
@@ -2738,10 +2738,10 @@
         <v>1.390162</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>8.772845999999999</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>6.31809</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>34.54586</v>
@@ -3482,10 +3482,10 @@
         <v>0.08788799999999999</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>8.963293</v>
+        <v>0.190447</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>6.577266</v>
+        <v>0.259176</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.214304</v>
@@ -12146,7 +12146,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -25926,7 +25926,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -30909,7 +30909,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -31002,7 +31002,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">

--- a/output/pdf_financials_xlsx/LA.xlsx
+++ b/output/pdf_financials_xlsx/LA.xlsx
@@ -799,19 +799,19 @@
         <v>0.594174</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.417933</v>
+        <v>0.887957</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.504812</v>
+        <v>2.920556</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1.483283</v>
+        <v>2.481782</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.8828549999999999</v>
+        <v>1.484761</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.859618</v>
+        <v>1.470997</v>
       </c>
     </row>
     <row r="8">
@@ -1003,7 +1003,7 @@
         <v>5.460817</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.859618</v>
+        <v>1.470997</v>
       </c>
     </row>
     <row r="11">
@@ -1439,19 +1439,19 @@
         <v>0.149609</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.41</v>
+        <v>-0.41</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-2.832199</v>
+        <v>2.832199</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1.817743</v>
+        <v>-1.817743</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>5.979686</v>
+        <v>-5.979686</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>-0.415032</v>
+        <v>0.415032</v>
       </c>
     </row>
     <row r="18">
@@ -7355,19 +7355,19 @@
         <v>0</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.267854</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.745044</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>1.093685</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>1.344452</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>1.67922</v>
       </c>
     </row>
     <row r="111">
@@ -7395,13 +7395,13 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.038817</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006603</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000378</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
@@ -8895,13 +8895,13 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.038817</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006603</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000378</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -8959,13 +8959,13 @@
         <v>-0.803518</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.603456</v>
+        <v>-0.642273</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.378315</v>
+        <v>-0.384918</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.131219</v>
+        <v>-0.131597</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-1.212386</v>
@@ -15722,7 +15722,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -15817,7 +15821,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -20238,7 +20246,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -23237,7 +23249,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -23429,7 +23445,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -23732,7 +23752,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -24233,7 +24257,11 @@
           <t>Consulting, salaries, management and directors’ fees 9</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -26219,7 +26247,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -26811,7 +26843,11 @@
           <t>Consulting, salaries, management and directors’ fees 9</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -28381,7 +28417,11 @@
           <t>Deferred income tax recovery (expense) 13</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -29640,7 +29680,11 @@
           <t>Deferred income tax recovery (expense) 13</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
